--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484821_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484821_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.0536</v>
+        <v>-0.8058</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0638</v>
+        <v>1.2586</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1173</v>
+        <v>-2.0644</v>
       </c>
       <c r="G2" t="n">
         <v>-0.0323</v>
@@ -610,13 +610,13 @@
         <v>0.9435</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7195</v>
+        <v>-0.4717</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3992</v>
+        <v>-0.2043</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3204</v>
+        <v>-0.2674</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2452</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.0969</v>
+        <v>-2.0137</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0682</v>
+        <v>1.6011</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.1651</v>
+        <v>-3.6148</v>
       </c>
       <c r="G3" t="n">
         <v>-1.4073</v>
@@ -688,13 +688,13 @@
         <v>1.6983</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7366</v>
+        <v>-0.1802</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3832</v>
+        <v>-0.0838</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3534</v>
+        <v>-0.0963</v>
       </c>
       <c r="V3" t="n">
         <v>-1.181</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.0443</v>
+        <v>-2.1829</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9781</v>
+        <v>1.9982</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.0224</v>
+        <v>-4.1811</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6849</v>
@@ -766,13 +766,13 @@
         <v>0.7548</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2251</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.074</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1511</v>
+        <v>-0.0076</v>
       </c>
       <c r="V4" t="n">
         <v>-2.1506</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.7145</v>
+        <v>-2.2962</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.0017</v>
+        <v>-1.6893</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7127</v>
+        <v>-0.6069</v>
       </c>
       <c r="G5" t="n">
         <v>0.0751</v>
@@ -844,13 +844,13 @@
         <v>1.3209</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7895</v>
+        <v>-0.3712</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6931</v>
+        <v>-0.3807</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0964</v>
+        <v>0.0094</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3018</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.1504</v>
+        <v>-3.6367</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7781</v>
+        <v>-0.2909</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.3723</v>
+        <v>-3.3458</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6438</v>
@@ -922,13 +922,13 @@
         <v>1.6983</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3744</v>
+        <v>-0.8608</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8107</v>
+        <v>-0.3235</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5637</v>
+        <v>-0.5372</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.6863</v>
+        <v>-4.8993</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0794</v>
+        <v>1.7871</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.7657</v>
+        <v>-6.6863</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2401</v>
@@ -1000,13 +1000,13 @@
         <v>2.2644</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8877</v>
+        <v>-1.1006</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0994</v>
+        <v>-0.3917</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7882</v>
+        <v>-0.7089</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8603</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.6429</v>
+        <v>-5.1415</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9741</v>
+        <v>-2.5256</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6688</v>
+        <v>-2.6159</v>
       </c>
       <c r="G8" t="n">
         <v>-3.6025</v>
@@ -1078,13 +1078,13 @@
         <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9082</v>
+        <v>-0.4068</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.458</v>
+        <v>-0.0094</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4503</v>
+        <v>-0.3974</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VAICIUNAS</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.9555</v>
+        <v>-5.6086</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1458</v>
+        <v>-2.9902</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.8098</v>
+        <v>-2.6184</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4166</v>
+        <v>-5.8274</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.8801</v>
+        <v>-3.7142</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4635</v>
+        <v>-2.1132</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2574</v>
+        <v>-1.6946</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8077</v>
+        <v>-1.1614</v>
       </c>
       <c r="L9" t="n">
-        <v>2.065</v>
+        <v>-0.5332</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.674</v>
+        <v>-4.1328</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.0725</v>
+        <v>-2.5528</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6015</v>
+        <v>-1.58</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0757</v>
+        <v>0.7548</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.774</v>
+        <v>-1.1322</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6983</v>
+        <v>1.887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5273</v>
+        <v>-1.2227</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3709</v>
+        <v>-0.786</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8982</v>
+        <v>-0.4367</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.6868</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X9" t="n">
         <v>0.06419999999999999</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>J. GARCIA CORBI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.0307</v>
+        <v>-6.1167</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4388</v>
+        <v>-1.8532</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5919</v>
+        <v>-4.2635</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.8274</v>
+        <v>-4.4503</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.7142</v>
+        <v>-3.078</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1132</v>
+        <v>-1.3723</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6946</v>
+        <v>-1.6942</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1614</v>
+        <v>-1.8587</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5332</v>
+        <v>0.1645</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.1328</v>
+        <v>-2.7561</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.5528</v>
+        <v>-1.2193</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.58</v>
+        <v>-1.5369</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7548</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R10" t="n">
-        <v>1.887</v>
+        <v>0.9435</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6448</v>
+        <v>-0.1455</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2345</v>
+        <v>-0.1208</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4103</v>
+        <v>-0.0247</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6868</v>
+        <v>-0.5774</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6226</v>
+        <v>1.8488</v>
       </c>
       <c r="X10" t="n">
-        <v>0.06419999999999999</v>
+        <v>-2.4262</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GARCIA CORBI</t>
+          <t>A. VAICIUNAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1453</v>
+        <v>-6.2311</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7759</v>
+        <v>-2.6329</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.3694</v>
+        <v>-3.5981</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.4503</v>
+        <v>-3.4166</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.078</v>
+        <v>-3.8801</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3723</v>
+        <v>0.4635</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6942</v>
+        <v>1.2574</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8587</v>
+        <v>-0.8077</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1645</v>
+        <v>2.065</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7561</v>
+        <v>-4.674</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2193</v>
+        <v>-3.0725</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5369</v>
+        <v>-1.6015</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9435</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.174</v>
+        <v>-0.8028999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0436</v>
+        <v>-0.1163</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1305</v>
+        <v>-0.6866</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5774</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8488</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4262</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-39.5204</v>
+        <v>-38.9325</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.924899999999999</v>
+        <v>-5.3371</v>
       </c>
       <c r="F12" t="n">
-        <v>-33.5954</v>
+        <v>-33.5952</v>
       </c>
       <c r="G12" t="n">
         <v>-22.2301</v>
@@ -1360,16 +1360,16 @@
         <v>-15.5189</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.711200000000001</v>
+        <v>-6.7112</v>
       </c>
       <c r="J12" t="n">
         <v>11.8371</v>
       </c>
       <c r="K12" t="n">
-        <v>4.155399999999999</v>
+        <v>4.1554</v>
       </c>
       <c r="L12" t="n">
-        <v>7.681500000000001</v>
+        <v>7.6815</v>
       </c>
       <c r="M12" t="n">
         <v>-34.0671</v>
@@ -1381,7 +1381,7 @@
         <v>-14.3928</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.660999999999999</v>
+        <v>-5.661</v>
       </c>
       <c r="Q12" t="n">
         <v>-19.8135</v>
@@ -1390,13 +1390,13 @@
         <v>14.1525</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.063700000000001</v>
+        <v>-5.4759</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.910400000000001</v>
+        <v>-2.3223</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.1535</v>
+        <v>-3.1534</v>
       </c>
       <c r="V12" t="n">
         <v>-5.565300000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.7742</v>
+        <v>5.5415</v>
       </c>
       <c r="E13" t="n">
-        <v>6.009</v>
+        <v>4.9543</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7653</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7761</v>
+        <v>5.5876</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5333</v>
+        <v>0.1996</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2428</v>
+        <v>5.388</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3576</v>
+        <v>6.5848</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7946</v>
+        <v>0.8507</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5629</v>
+        <v>5.7341</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5815</v>
+        <v>-0.9972</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2614</v>
+        <v>-0.6511</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3202</v>
+        <v>-0.3461</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6983</v>
+        <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6024</v>
+        <v>0.5576</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9539</v>
+        <v>0.2566</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6485</v>
+        <v>0.301</v>
       </c>
       <c r="V13" t="n">
-        <v>1.528</v>
+        <v>-0.6036</v>
       </c>
       <c r="W13" t="n">
-        <v>1.528</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1446</v>
+        <v>5.5058</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7037</v>
+        <v>3.742</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4409</v>
+        <v>1.7637</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1759</v>
+        <v>4.7703</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6644</v>
+        <v>4.6509</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8403</v>
+        <v>0.1194</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9618</v>
+        <v>4.5326</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.09470000000000001</v>
+        <v>4.3269</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0565</v>
+        <v>0.2057</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7859</v>
+        <v>0.2378</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5697</v>
+        <v>0.324</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2162</v>
+        <v>-0.0863</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R14" t="n">
         <v>2.2644</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4973</v>
+        <v>0.6597</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5349</v>
+        <v>0.153</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9624</v>
+        <v>0.5068</v>
       </c>
       <c r="V14" t="n">
-        <v>3.094</v>
+        <v>-1.2452</v>
       </c>
       <c r="W14" t="n">
-        <v>3.094</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2719</v>
+        <v>5.4903</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7651</v>
+        <v>3.314</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5068</v>
+        <v>2.1763</v>
       </c>
       <c r="G15" t="n">
-        <v>5.9162</v>
+        <v>1.1759</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3119</v>
+        <v>-0.6644</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6042</v>
+        <v>1.8403</v>
       </c>
       <c r="J15" t="n">
-        <v>7.4163</v>
+        <v>1.9618</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4919</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>3.9244</v>
+        <v>2.0565</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5001</v>
+        <v>-0.7859</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.18</v>
+        <v>-0.5697</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3202</v>
+        <v>-0.2162</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R15" t="n">
-        <v>1.887</v>
+        <v>2.2644</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2992</v>
+        <v>0.843</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1793</v>
+        <v>0.1451</v>
       </c>
       <c r="U15" t="n">
-        <v>0.12</v>
+        <v>0.6978</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>3.094</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.094</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8729</v>
+        <v>5.4283</v>
       </c>
       <c r="E16" t="n">
-        <v>4.7595</v>
+        <v>4.7651</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1134</v>
+        <v>0.6632</v>
       </c>
       <c r="G16" t="n">
-        <v>5.5876</v>
+        <v>5.9162</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1996</v>
+        <v>3.3119</v>
       </c>
       <c r="I16" t="n">
-        <v>5.388</v>
+        <v>2.6042</v>
       </c>
       <c r="J16" t="n">
-        <v>6.5848</v>
+        <v>7.4163</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8507</v>
+        <v>3.4919</v>
       </c>
       <c r="L16" t="n">
-        <v>5.7341</v>
+        <v>3.9244</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9972</v>
+        <v>-1.5001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6511</v>
+        <v>-0.18</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3461</v>
+        <v>-1.3202</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R16" t="n">
         <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1111</v>
+        <v>0.4556</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0617</v>
+        <v>0.1793</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1728</v>
+        <v>0.2763</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4028</v>
+        <v>4.8834</v>
       </c>
       <c r="E17" t="n">
-        <v>3.06</v>
+        <v>4.2552</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3428</v>
+        <v>0.6283</v>
       </c>
       <c r="G17" t="n">
-        <v>4.7703</v>
+        <v>2.7761</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6509</v>
+        <v>2.5333</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1194</v>
+        <v>0.2428</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5326</v>
+        <v>4.3576</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3269</v>
+        <v>2.7946</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2057</v>
+        <v>1.5629</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2378</v>
+        <v>-1.5815</v>
       </c>
       <c r="N17" t="n">
-        <v>0.324</v>
+        <v>-0.2614</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0863</v>
+        <v>-1.3202</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3209</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2644</v>
+        <v>1.6983</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4432</v>
+        <v>1.7115</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5291</v>
+        <v>1.2001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0859</v>
+        <v>0.5115</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2452</v>
+        <v>1.528</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.528</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.1432</v>
+        <v>4.8564</v>
       </c>
       <c r="E18" t="n">
-        <v>3.9609</v>
+        <v>4.2532</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1823</v>
+        <v>0.6032</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4556</v>
@@ -1858,13 +1858,13 @@
         <v>2.0757</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0517</v>
+        <v>0.765</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1793</v>
+        <v>0.4716</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1275</v>
+        <v>0.2934</v>
       </c>
       <c r="V18" t="n">
         <v>3.4148</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.7169</v>
+        <v>3.2649</v>
       </c>
       <c r="E19" t="n">
         <v>0.5144</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2025</v>
+        <v>2.7504</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8032</v>
@@ -1936,13 +1936,13 @@
         <v>1.887</v>
       </c>
       <c r="S19" t="n">
-        <v>1.388</v>
+        <v>0.9359</v>
       </c>
       <c r="T19" t="n">
         <v>0.1205</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2675</v>
+        <v>0.8154</v>
       </c>
       <c r="V19" t="n">
         <v>1.2452</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5665</v>
+        <v>2.6904</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5603</v>
+        <v>3.9607</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9938</v>
+        <v>-1.2703</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6359</v>
+        <v>1.2195</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7788</v>
+        <v>0.3929</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.143</v>
+        <v>0.8266</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6185</v>
+        <v>3.5648</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8526</v>
+        <v>1.548</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7659</v>
+        <v>2.0168</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9826</v>
+        <v>-2.3453</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0737</v>
+        <v>-1.1551</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9089</v>
+        <v>-1.1902</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3209</v>
+        <v>2.2644</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1193</v>
+        <v>0.1501</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8288</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2905</v>
+        <v>0.0559</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6226</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4552</v>
+        <v>1.7183</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2786</v>
+        <v>1.3737</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8234</v>
+        <v>0.3446</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2195</v>
+        <v>0.4075</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3929</v>
+        <v>0.115</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8266</v>
+        <v>0.2924</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5648</v>
+        <v>1.5718</v>
       </c>
       <c r="K21" t="n">
-        <v>1.548</v>
+        <v>0.1323</v>
       </c>
       <c r="L21" t="n">
-        <v>2.0168</v>
+        <v>1.4396</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3453</v>
+        <v>-1.1643</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1551</v>
+        <v>-0.0172</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1902</v>
+        <v>-1.1471</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3209</v>
+        <v>2.2644</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>2.2644</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0852</v>
+        <v>0.2916</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5879</v>
+        <v>-0.1981</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4973</v>
+        <v>0.4897</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>-1.2452</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.1722</v>
+        <v>1.4402</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9839</v>
+        <v>2.4628</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1882</v>
+        <v>-1.0226</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4075</v>
+        <v>1.6359</v>
       </c>
       <c r="H22" t="n">
-        <v>0.115</v>
+        <v>1.7788</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2924</v>
+        <v>-0.143</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5718</v>
+        <v>3.6185</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1323</v>
+        <v>2.8526</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4396</v>
+        <v>0.7659</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1643</v>
+        <v>-1.9826</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0172</v>
+        <v>-1.0737</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1471</v>
+        <v>-0.9089</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2644</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2644</v>
+        <v>1.3209</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2545</v>
+        <v>0.993</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5879</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3334</v>
+        <v>0.2616</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2452</v>
+        <v>-0.6226</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2452</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>39.5204</v>
+        <v>40.8195</v>
       </c>
       <c r="E23" t="n">
         <v>33.5954</v>
       </c>
       <c r="F23" t="n">
-        <v>5.925000000000001</v>
+        <v>7.224000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>22.2302</v>
@@ -2218,7 +2218,7 @@
         <v>15.5189</v>
       </c>
       <c r="I23" t="n">
-        <v>6.7111</v>
+        <v>6.711099999999998</v>
       </c>
       <c r="J23" t="n">
         <v>34.0673</v>
@@ -2248,13 +2248,13 @@
         <v>19.8135</v>
       </c>
       <c r="S23" t="n">
-        <v>6.0639</v>
+        <v>7.363</v>
       </c>
       <c r="T23" t="n">
-        <v>3.1535</v>
+        <v>3.1537</v>
       </c>
       <c r="U23" t="n">
-        <v>2.9106</v>
+        <v>4.2094</v>
       </c>
       <c r="V23" t="n">
         <v>5.5654</v>
